--- a/dataset/construct/dataset_splits/data_size/5_percent/tum/test.xlsx
+++ b/dataset/construct/dataset_splits/data_size/5_percent/tum/test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN67"/>
+  <dimension ref="A1:AK67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -643,80 +628,82 @@
         <v>88.78116967069739</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>27.1415823914336</v>
       </c>
       <c r="E2" t="n">
-        <v>27.1415823914336</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>211.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>195</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>127.4</v>
       </c>
       <c r="K2" t="n">
-        <v>211.5</v>
+        <v>533.9</v>
       </c>
       <c r="L2" t="n">
-        <v>195</v>
+        <v>21.4</v>
       </c>
       <c r="M2" t="n">
-        <v>127.4</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>533.9</v>
+        <v>7.3</v>
       </c>
       <c r="O2" t="n">
-        <v>21.4</v>
+        <v>28.7</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>28.7</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>24.9</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>25.082760376878</v>
       </c>
       <c r="X2" t="n">
-        <v>24.9</v>
+        <v>24.5626156992528</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.195652173913044</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>25.082760376878</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>24.5626156992528</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -728,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -737,18 +724,9 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
         <v>198</v>
       </c>
-      <c r="AN2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -763,83 +741,85 @@
         <v>85.58062140340201</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>27.0416441319632</v>
       </c>
       <c r="E3" t="n">
-        <v>27.0416441319632</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>43</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>691</v>
+      </c>
+      <c r="I3" t="n">
+        <v>379</v>
+      </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>245</v>
       </c>
       <c r="K3" t="n">
-        <v>691</v>
+        <v>1315</v>
       </c>
       <c r="L3" t="n">
-        <v>379</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="N3" t="n">
-        <v>1315</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>24.8281130634072</v>
       </c>
       <c r="X3" t="n">
-        <v>24.4</v>
+        <v>24.3805715703063</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.212454212454212</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>24.8281130634072</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.3805715703063</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>0</v>
@@ -848,27 +828,18 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>112</v>
-      </c>
-      <c r="AN3" t="n">
         <v>222</v>
       </c>
     </row>
@@ -885,80 +856,82 @@
         <v>64.8277587015489</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>25.6055363321799</v>
       </c>
       <c r="E4" t="n">
-        <v>25.6055363321799</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+        <v>553</v>
+      </c>
+      <c r="I4" t="n">
+        <v>592</v>
+      </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="K4" t="n">
-        <v>553</v>
+        <v>1200</v>
       </c>
       <c r="L4" t="n">
-        <v>592</v>
+        <v>88</v>
       </c>
       <c r="M4" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="N4" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="P4" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>21.9</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>22.1543162719633</v>
       </c>
       <c r="X4" t="n">
-        <v>21.9</v>
+        <v>21.2868030290747</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.295719844357977</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.1543162719633</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.2868030290747</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -967,30 +940,21 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN4" t="n">
         <v>174</v>
       </c>
     </row>
@@ -1007,77 +971,79 @@
         <v>84.1220203374148</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>25.1558956916099</v>
       </c>
       <c r="E5" t="n">
-        <v>25.1558956916099</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>55</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>878.7</v>
+      </c>
+      <c r="I5" t="n">
+        <v>287.2</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>397</v>
       </c>
       <c r="K5" t="n">
-        <v>878.7</v>
+        <v>1562.9</v>
       </c>
       <c r="L5" t="n">
-        <v>287.2</v>
+        <v>38</v>
       </c>
       <c r="M5" t="n">
-        <v>397</v>
+        <v>41</v>
       </c>
       <c r="N5" t="n">
-        <v>1562.9</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="P5" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>24.7</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>26.1013496307614</v>
       </c>
       <c r="X5" t="n">
-        <v>24.7</v>
+        <v>25.126169248131</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.319727891156463</v>
+        <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>26.1013496307614</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>25.126169248131</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1086,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1101,18 +1067,9 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
         <v>158</v>
       </c>
-      <c r="AN5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1127,35 +1084,37 @@
         <v>81.8413179709484</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>30.795847750865</v>
       </c>
       <c r="E6" t="n">
-        <v>30.795847750865</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>60</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
+        <v>534.9</v>
+      </c>
+      <c r="I6" t="n">
+        <v>188.6</v>
+      </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>224.4</v>
       </c>
       <c r="K6" t="n">
-        <v>534.9</v>
+        <v>947.9</v>
       </c>
       <c r="L6" t="n">
-        <v>188.6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>224.4</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>947.9</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1173,37 +1132,37 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>24.6689584924879</v>
       </c>
       <c r="X6" t="n">
-        <v>24.8</v>
+        <v>23.5601735863367</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.277777777777778</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>24.6689584924879</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>23.5601735863367</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
@@ -1212,7 +1171,7 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
@@ -1221,24 +1180,15 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN6" t="n">
         <v>208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>474</v>
+        <v>1695</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1246,85 +1196,85 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>78.2075977577509</v>
+        <v>72.6859265913758</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>26.0374939913475</v>
       </c>
       <c r="E7" t="n">
-        <v>27.6816608996539</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>42</v>
+        <v>160.6</v>
       </c>
       <c r="I7" t="n">
-        <v>911</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>58.1</v>
       </c>
       <c r="K7" t="n">
-        <v>187</v>
+        <v>293.3</v>
       </c>
       <c r="L7" t="n">
-        <v>222</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>630</v>
+        <v>13.4</v>
       </c>
       <c r="O7" t="n">
-        <v>11</v>
+        <v>13.4</v>
       </c>
       <c r="P7" t="n">
-        <v>25</v>
+        <v>11.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>59</v>
+        <v>6.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>17.6</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>21.15</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>21.2312197606315</v>
       </c>
       <c r="X7" t="n">
-        <v>26.8</v>
+        <v>20.4044886078792</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.213333333333333</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>26.7379679144385</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>26.4345313179585</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1345,22 +1295,15 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+        <v>142</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1387</v>
+        <v>1584</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1368,41 +1311,43 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>89.14018851243441</v>
+        <v>90.1227350305473</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>32.8947368421052</v>
       </c>
       <c r="E8" t="n">
-        <v>25.78125</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>43</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
+        <v>132.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>101.7</v>
+      </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>107.1</v>
       </c>
       <c r="K8" t="n">
-        <v>46.3</v>
+        <v>341.5</v>
       </c>
       <c r="L8" t="n">
-        <v>42.8</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>31.7</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>120.8</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -1417,28 +1362,28 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>21.95</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>23.1410746116628</v>
       </c>
       <c r="X8" t="n">
-        <v>23.8</v>
+        <v>21.9926337013585</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.318021201413428</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>23.8731856378915</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.0715863589186</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1453,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
@@ -1465,18 +1410,11 @@
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
+        <v>152</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1491,76 +1429,76 @@
         <v>85.7122274507567</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>30.3397612488521</v>
       </c>
       <c r="E9" t="n">
-        <v>30.3397612488521</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
+        <v>546</v>
       </c>
       <c r="I9" t="n">
-        <v>2050</v>
+        <v>496</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>289</v>
       </c>
       <c r="K9" t="n">
-        <v>546</v>
+        <v>1331</v>
       </c>
       <c r="L9" t="n">
-        <v>496</v>
+        <v>131</v>
       </c>
       <c r="M9" t="n">
-        <v>289</v>
+        <v>21</v>
       </c>
       <c r="N9" t="n">
-        <v>1331</v>
+        <v>131</v>
       </c>
       <c r="O9" t="n">
-        <v>131</v>
+        <v>283</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="Q9" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>283</v>
+        <v>44</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>44</v>
+        <v>25.4</v>
       </c>
       <c r="V9" t="n">
-        <v>74</v>
+        <v>0.15</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>25.4647313470843</v>
       </c>
       <c r="X9" t="n">
-        <v>25.4</v>
+        <v>24.8715915644925</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.152727272727273</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>25.4647313470843</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>24.8715915644925</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1578,31 +1516,22 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM9" t="n">
         <v>98</v>
       </c>
-      <c r="AN9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1464</v>
+        <v>2607</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1610,83 +1539,85 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>86.0682524019571</v>
+        <v>81.77774745227769</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>28.1969212010364</v>
       </c>
       <c r="E10" t="n">
-        <v>31.25</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>60</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="I10" t="n">
+        <v>31</v>
+      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="K10" t="n">
-        <v>471.5</v>
+        <v>132</v>
       </c>
       <c r="L10" t="n">
-        <v>366.4</v>
+        <v>25</v>
       </c>
       <c r="M10" t="n">
-        <v>152.6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>990.5</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="P10" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>23.5</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>23.5867074102368</v>
       </c>
       <c r="X10" t="n">
-        <v>26.15</v>
+        <v>22.8860247016979</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.184027777777778</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>26.6743060860708</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>26.357378198087</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1695,7 +1626,7 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -1707,22 +1638,15 @@
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>82</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
+        <v>210</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>667</v>
+        <v>1677</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1730,79 +1654,79 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>84.9569007148833</v>
+        <v>82.4924465738839</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>29.3333333333333</v>
       </c>
       <c r="E11" t="n">
-        <v>27.0551508844953</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>44</v>
+        <v>112</v>
       </c>
       <c r="I11" t="n">
-        <v>1280</v>
+        <v>67</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="K11" t="n">
-        <v>122.4</v>
+        <v>238</v>
       </c>
       <c r="L11" t="n">
-        <v>112.1</v>
+        <v>25</v>
       </c>
       <c r="M11" t="n">
-        <v>504</v>
+        <v>9</v>
       </c>
       <c r="N11" t="n">
-        <v>738.5</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
-        <v>6.5</v>
+        <v>46</v>
       </c>
       <c r="P11" t="n">
-        <v>35.9</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>99.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>142.2</v>
+        <v>15</v>
       </c>
       <c r="S11" t="n">
-        <v>5.4</v>
+        <v>15</v>
       </c>
       <c r="T11" t="n">
-        <v>7.6</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>85.3</v>
+        <v>21.8</v>
       </c>
       <c r="V11" t="n">
-        <v>98.3</v>
+        <v>0.15</v>
       </c>
       <c r="W11" t="n">
-        <v>2</v>
+        <v>21.9633307868602</v>
       </c>
       <c r="X11" t="n">
-        <v>22.3</v>
+        <v>21.7013276779863</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.149377593360996</v>
+        <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.7591036414566</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>22.6146780197282</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -1817,7 +1741,7 @@
         <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -1829,19 +1753,10 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>152</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>200</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12">
@@ -1857,82 +1772,82 @@
         <v>89.7616320632748</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>26.1965927528393</v>
       </c>
       <c r="E12" t="n">
-        <v>26.1965927528393</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>55</v>
+        <v>506</v>
       </c>
       <c r="I12" t="n">
-        <v>1280</v>
+        <v>689</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>481</v>
       </c>
       <c r="K12" t="n">
-        <v>506</v>
+        <v>1676</v>
       </c>
       <c r="L12" t="n">
-        <v>689</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>481</v>
+        <v>85</v>
       </c>
       <c r="N12" t="n">
-        <v>1676</v>
+        <v>109</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="P12" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>20</v>
+        <v>23.1</v>
       </c>
       <c r="V12" t="n">
-        <v>20</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>23.2365673542144</v>
       </c>
       <c r="X12" t="n">
-        <v>23.1</v>
+        <v>23.0660688205498</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0987654320987655</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.2365673542144</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>23.0660688205498</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -1941,30 +1856,21 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>82</v>
-      </c>
-      <c r="AN12" t="n">
         <v>160</v>
       </c>
     </row>
@@ -1981,88 +1887,88 @@
         <v>64.078326710523</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>27.7703126399713</v>
       </c>
       <c r="E13" t="n">
-        <v>27.7703126399713</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>21</v>
+        <v>1098.7</v>
       </c>
       <c r="I13" t="n">
-        <v>3660</v>
+        <v>660.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>510.2</v>
       </c>
       <c r="K13" t="n">
-        <v>1098.7</v>
+        <v>2269</v>
       </c>
       <c r="L13" t="n">
-        <v>660.1</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>510.2</v>
+        <v>47.8</v>
       </c>
       <c r="N13" t="n">
-        <v>2269</v>
+        <v>30.2</v>
       </c>
       <c r="O13" t="n">
-        <v>71.90000000000001</v>
+        <v>149.9</v>
       </c>
       <c r="P13" t="n">
-        <v>47.8</v>
+        <v>7.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>30.2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>149.9</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>7.3</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>30.15</v>
       </c>
       <c r="V13" t="n">
-        <v>7.3</v>
+        <v>0.24</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>30.3030303030303</v>
       </c>
       <c r="X13" t="n">
-        <v>30.15</v>
+        <v>29.817322856274</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.236842105263158</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>30.3030303030303</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>29.817322856274</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2077,24 +1983,15 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN13" t="n">
         <v>140</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>609</v>
+        <v>1464</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2102,85 +1999,85 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>88.2475587497148</v>
+        <v>86.0682524019571</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="E14" t="n">
-        <v>22.8928199791883</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>60</v>
+        <v>471.5</v>
       </c>
       <c r="I14" t="n">
-        <v>4240</v>
+        <v>366.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>152.6</v>
       </c>
       <c r="K14" t="n">
-        <v>590</v>
+        <v>990.5</v>
       </c>
       <c r="L14" t="n">
-        <v>257</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>274</v>
+        <v>7.3</v>
       </c>
       <c r="N14" t="n">
-        <v>1121</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>87</v>
+        <v>7.3</v>
       </c>
       <c r="P14" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>24</v>
+        <v>26.15</v>
       </c>
       <c r="V14" t="n">
-        <v>35</v>
+        <v>0.18</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>26.6743060860708</v>
       </c>
       <c r="X14" t="n">
-        <v>23.2</v>
+        <v>26.357378198087</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.180392156862745</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>23.6822001527884</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.2584038731959</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2189,10 +2086,10 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
@@ -2201,20 +2098,9 @@
         <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>102</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>200</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="AK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2229,83 +2115,85 @@
         <v>81.0768854095368</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>28.125</v>
       </c>
       <c r="E15" t="n">
-        <v>28.125</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>55</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
+        <v>545.5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>517</v>
+      </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>545.5</v>
+        <v>1142.9</v>
       </c>
       <c r="L15" t="n">
-        <v>517</v>
+        <v>268.2</v>
       </c>
       <c r="M15" t="n">
-        <v>80.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>1142.9</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>268.2</v>
+        <v>347.1</v>
       </c>
       <c r="P15" t="n">
-        <v>78.90000000000001</v>
+        <v>259.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>39.1</v>
       </c>
       <c r="R15" t="n">
-        <v>347.1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>259.8</v>
+        <v>298.9</v>
       </c>
       <c r="T15" t="n">
-        <v>39.1</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>23.85</v>
       </c>
       <c r="V15" t="n">
-        <v>298.9</v>
+        <v>0.09</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>23.8413547237077</v>
       </c>
       <c r="X15" t="n">
-        <v>23.85</v>
+        <v>23.6303013331054</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.0920000000000001</v>
+        <v>1</v>
       </c>
       <c r="Z15" t="n">
-        <v>23.8413547237077</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>23.6303013331054</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2314,7 +2202,7 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2323,18 +2211,9 @@
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN15" t="n">
         <v>206</v>
       </c>
     </row>
@@ -2351,79 +2230,79 @@
         <v>79.6806004258879</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>21.2228082768952</v>
       </c>
       <c r="E16" t="n">
-        <v>21.2228082768952</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>1074</v>
       </c>
       <c r="I16" t="n">
-        <v>3500</v>
+        <v>510</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>703</v>
       </c>
       <c r="K16" t="n">
-        <v>1074</v>
+        <v>2287</v>
       </c>
       <c r="L16" t="n">
-        <v>510</v>
+        <v>55.5</v>
       </c>
       <c r="M16" t="n">
-        <v>703</v>
+        <v>43.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2287</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>55.5</v>
+        <v>98.7</v>
       </c>
       <c r="P16" t="n">
-        <v>43.2</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="R16" t="n">
-        <v>98.7</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T16" t="n">
-        <v>5.7</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>26.85</v>
       </c>
       <c r="V16" t="n">
-        <v>5.7</v>
+        <v>0.23</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>27.0562770562771</v>
       </c>
       <c r="X16" t="n">
-        <v>26.85</v>
+        <v>26.6980447139561</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.233552631578947</v>
+        <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>27.0562770562771</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>26.6980447139561</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2432,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2447,18 +2326,9 @@
         <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="AK16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>144</v>
-      </c>
-      <c r="AN16" t="n">
         <v>214</v>
       </c>
     </row>
@@ -2475,74 +2345,76 @@
         <v>80.44446586559179</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>28.6989795918367</v>
       </c>
       <c r="E17" t="n">
-        <v>28.6989795918367</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>50</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>1389</v>
+      </c>
+      <c r="I17" t="n">
+        <v>555.3</v>
+      </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>527.9</v>
       </c>
       <c r="K17" t="n">
-        <v>1389</v>
+        <v>2472.2</v>
       </c>
       <c r="L17" t="n">
-        <v>555.3</v>
+        <v>199.1</v>
       </c>
       <c r="M17" t="n">
-        <v>527.9</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>2472.2</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>199.1</v>
+        <v>295.2</v>
       </c>
       <c r="P17" t="n">
-        <v>96.09999999999999</v>
+        <v>111.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="R17" t="n">
-        <v>295.2</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>111.1</v>
+        <v>119.5</v>
       </c>
       <c r="T17" t="n">
-        <v>8.4</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>27.05</v>
       </c>
       <c r="V17" t="n">
-        <v>119.5</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>27.0244461420932</v>
       </c>
       <c r="X17" t="n">
-        <v>27.05</v>
+        <v>26.5330558887474</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.196666666666667</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>27.0244461420932</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>26.5330558887474</v>
+        <v>1</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2551,10 +2423,10 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2568,21 +2440,12 @@
       <c r="AI17" t="n">
         <v>0</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2590,85 +2453,85 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>84.1788995360864</v>
+        <v>83.724576013385</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>28.515625</v>
       </c>
       <c r="E18" t="n">
-        <v>26.5731292517006</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
+        <v>307.1</v>
       </c>
       <c r="I18" t="n">
-        <v>2760</v>
+        <v>345</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>87.2</v>
       </c>
       <c r="K18" t="n">
-        <v>983</v>
+        <v>739.3000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>431</v>
+        <v>45.5</v>
       </c>
       <c r="M18" t="n">
-        <v>252</v>
+        <v>7.3</v>
       </c>
       <c r="N18" t="n">
-        <v>1666</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
-        <v>146</v>
+        <v>55.9</v>
       </c>
       <c r="P18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>274</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>24.05</v>
       </c>
       <c r="V18" t="n">
-        <v>6</v>
+        <v>0.11</v>
       </c>
       <c r="W18" t="n">
-        <v>2</v>
+        <v>24.3188184364655</v>
       </c>
       <c r="X18" t="n">
-        <v>21.55</v>
+        <v>24.152404368873</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.204166666666667</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.6450216450216</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>20.9553534365411</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2689,24 +2552,15 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>170</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2397</v>
+        <v>636</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2714,43 +2568,43 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>76.83366827642151</v>
+        <v>81.9098752756864</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="E19" t="n">
-        <v>29.3847566574839</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>25</v>
+        <v>607.7</v>
       </c>
       <c r="I19" t="n">
-        <v>21800</v>
+        <v>229.5</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>268.5</v>
       </c>
       <c r="K19" t="n">
-        <v>818.8</v>
+        <v>1105.7</v>
       </c>
       <c r="L19" t="n">
-        <v>45.1</v>
+        <v>26.8</v>
       </c>
       <c r="M19" t="n">
-        <v>9.9</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>873.8</v>
+        <v>20.3</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>47.1</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -2765,34 +2619,34 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>24.45</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>24.3824802648332</v>
       </c>
       <c r="X19" t="n">
-        <v>24.3</v>
+        <v>24.1734751727661</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.116279069767442</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>24.5416348357525</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>24.4249070315066</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -2813,19 +2667,10 @@
         <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
         <v>146</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>196</v>
       </c>
     </row>
     <row r="20">
@@ -2841,85 +2686,85 @@
         <v>92.46904327325269</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>27.1111111111111</v>
       </c>
       <c r="E20" t="n">
-        <v>27.1111111111111</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>40</v>
+        <v>312</v>
       </c>
       <c r="I20" t="n">
-        <v>13300</v>
+        <v>314</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>440</v>
       </c>
       <c r="K20" t="n">
-        <v>312</v>
+        <v>1066</v>
       </c>
       <c r="L20" t="n">
-        <v>314</v>
+        <v>16</v>
       </c>
       <c r="M20" t="n">
-        <v>440</v>
+        <v>26</v>
       </c>
       <c r="N20" t="n">
-        <v>1066</v>
+        <v>114</v>
       </c>
       <c r="O20" t="n">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="P20" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>114</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>112</v>
+        <v>23.6</v>
       </c>
       <c r="V20" t="n">
-        <v>112</v>
+        <v>0.18</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X20" t="n">
-        <v>23.6</v>
+        <v>23.5844721732425</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.184615384615385</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>23.8731856378915</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>23.5844721732425</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE20" t="n">
         <v>0</v>
@@ -2928,33 +2773,24 @@
         <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>102</v>
-      </c>
-      <c r="AN20" t="n">
         <v>230</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>577</v>
+        <v>705</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2962,79 +2798,79 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>85.0743345501559</v>
+        <v>87.1852574340254</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>21.6412742382271</v>
       </c>
       <c r="E21" t="n">
-        <v>25.5593291551416</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>54</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>9910</v>
+        <v>77.2</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>124.9</v>
       </c>
       <c r="K21" t="n">
-        <v>903.7</v>
+        <v>298.5</v>
       </c>
       <c r="L21" t="n">
-        <v>809.6</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>747.3</v>
+        <v>7.7</v>
       </c>
       <c r="N21" t="n">
-        <v>2460.6</v>
+        <v>50.6</v>
       </c>
       <c r="O21" t="n">
-        <v>6.1</v>
+        <v>58.3</v>
       </c>
       <c r="P21" t="n">
-        <v>58.9</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>146.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>211.1</v>
+        <v>64.7</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>64.7</v>
       </c>
       <c r="T21" t="n">
-        <v>9.199999999999999</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
-        <v>63.5</v>
+        <v>20.25</v>
       </c>
       <c r="V21" t="n">
-        <v>72.7</v>
+        <v>0.22</v>
       </c>
       <c r="W21" t="n">
-        <v>2</v>
+        <v>20.3081232492997</v>
       </c>
       <c r="X21" t="n">
-        <v>24.7</v>
+        <v>20.0267116219144</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.203636363636364</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>24.7962821492233</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>24.4717629124263</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3058,22 +2894,13 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>114</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>146</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22">
@@ -3089,114 +2916,105 @@
         <v>80.32943569853219</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>29.9136168004639</v>
       </c>
       <c r="E22" t="n">
-        <v>29.9136168004639</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="G22" t="n">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>48</v>
+        <v>624</v>
       </c>
       <c r="I22" t="n">
-        <v>2080</v>
+        <v>725</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>612</v>
       </c>
       <c r="K22" t="n">
-        <v>624</v>
+        <v>1961</v>
       </c>
       <c r="L22" t="n">
-        <v>725</v>
+        <v>220</v>
       </c>
       <c r="M22" t="n">
-        <v>612</v>
+        <v>16</v>
       </c>
       <c r="N22" t="n">
-        <v>1961</v>
+        <v>160</v>
       </c>
       <c r="O22" t="n">
-        <v>220</v>
+        <v>396</v>
       </c>
       <c r="P22" t="n">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>113</v>
+      </c>
+      <c r="S22" t="n">
+        <v>241</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W22" t="n">
+        <v>28.9661319073084</v>
+      </c>
+      <c r="X22" t="n">
+        <v>27.1706131660289</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
         <v>160</v>
       </c>
-      <c r="R22" t="n">
-        <v>396</v>
-      </c>
-      <c r="S22" t="n">
-        <v>128</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>113</v>
-      </c>
-      <c r="V22" t="n">
-        <v>241</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1</v>
-      </c>
-      <c r="X22" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0.320987654320988</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>28.9661319073084</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>27.1706131660289</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3211,79 +3029,79 @@
         <v>78.3116140010647</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>39.5484045429962</v>
       </c>
       <c r="E23" t="n">
-        <v>39.5484045429962</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>55</v>
+        <v>756.6</v>
       </c>
       <c r="I23" t="n">
-        <v>319</v>
+        <v>150.9</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>197.7</v>
       </c>
       <c r="K23" t="n">
-        <v>756.6</v>
+        <v>1105.2</v>
       </c>
       <c r="L23" t="n">
-        <v>150.9</v>
+        <v>179</v>
       </c>
       <c r="M23" t="n">
-        <v>197.7</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>1105.2</v>
+        <v>11.7</v>
       </c>
       <c r="O23" t="n">
-        <v>179</v>
+        <v>190.7</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>60.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>11.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>190.7</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>60.6</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>26.3</v>
       </c>
       <c r="V23" t="n">
-        <v>60.6</v>
+        <v>0.26</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>27.2472625413802</v>
       </c>
       <c r="X23" t="n">
-        <v>26.3</v>
+        <v>26.6574900946335</v>
       </c>
       <c r="Y23" t="n">
-        <v>0.258278145695364</v>
+        <v>1</v>
       </c>
       <c r="Z23" t="n">
-        <v>27.2472625413802</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>26.6574900946335</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3292,7 +3110,7 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3307,18 +3125,9 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="AK23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>134</v>
-      </c>
-      <c r="AN23" t="n">
         <v>216</v>
       </c>
     </row>
@@ -3335,86 +3144,88 @@
         <v>70.78022333764289</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>27.7769298861451</v>
       </c>
       <c r="E24" t="n">
-        <v>27.7769298861451</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G24" t="n">
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>50</v>
-      </c>
-      <c r="I24" t="inlineStr"/>
+        <v>327.4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>575.9</v>
+      </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>128.9</v>
       </c>
       <c r="K24" t="n">
-        <v>327.4</v>
+        <v>1032.2</v>
       </c>
       <c r="L24" t="n">
-        <v>575.9</v>
+        <v>35.2</v>
       </c>
       <c r="M24" t="n">
-        <v>128.9</v>
+        <v>27.2</v>
       </c>
       <c r="N24" t="n">
-        <v>1032.2</v>
+        <v>23.7</v>
       </c>
       <c r="O24" t="n">
-        <v>35.2</v>
+        <v>86.10000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>27.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>86.09999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="S24" t="n">
-        <v>8.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>5.7</v>
+        <v>29.05</v>
       </c>
       <c r="V24" t="n">
-        <v>14.5</v>
+        <v>0.13</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>29.3162719633308</v>
       </c>
       <c r="X24" t="n">
-        <v>29.05</v>
+        <v>29.0694474562021</v>
       </c>
       <c r="Y24" t="n">
-        <v>0.131832797427653</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>29.3162719633308</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>29.0694474562021</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3429,18 +3240,9 @@
         <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
         <v>94</v>
       </c>
-      <c r="AN24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3455,85 +3257,85 @@
         <v>86.45430070727809</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>26.813590449954</v>
       </c>
       <c r="E25" t="n">
-        <v>26.813590449954</v>
+        <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="I25" t="n">
-        <v>821</v>
+        <v>469</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>419</v>
       </c>
       <c r="K25" t="n">
-        <v>270</v>
+        <v>1158</v>
       </c>
       <c r="L25" t="n">
-        <v>469</v>
+        <v>78</v>
       </c>
       <c r="M25" t="n">
-        <v>419</v>
+        <v>139</v>
       </c>
       <c r="N25" t="n">
-        <v>1158</v>
+        <v>92</v>
       </c>
       <c r="O25" t="n">
-        <v>78</v>
+        <v>309</v>
       </c>
       <c r="P25" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="R25" t="n">
-        <v>309</v>
+        <v>33</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="T25" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>33</v>
+        <v>23.85</v>
       </c>
       <c r="V25" t="n">
-        <v>85</v>
+        <v>0.16</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X25" t="n">
-        <v>23.85</v>
+        <v>23.7458273423211</v>
       </c>
       <c r="Y25" t="n">
-        <v>0.158301158301158</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>24.1914947797301</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>23.7458273423211</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -3542,27 +3344,18 @@
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI25" t="n">
         <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN25" t="n">
         <v>220</v>
       </c>
     </row>
@@ -3579,37 +3372,37 @@
         <v>90.5060536606079</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>27.2173029467266</v>
       </c>
       <c r="E26" t="n">
-        <v>27.2173029467266</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>52</v>
+        <v>264</v>
       </c>
       <c r="I26" t="n">
-        <v>5650</v>
+        <v>260</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>449</v>
       </c>
       <c r="K26" t="n">
-        <v>264</v>
+        <v>973</v>
       </c>
       <c r="L26" t="n">
-        <v>260</v>
+        <v>18</v>
       </c>
       <c r="M26" t="n">
-        <v>449</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>973</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>18</v>
@@ -3621,40 +3414,40 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>24.95</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="W26" t="n">
-        <v>1</v>
+        <v>25.1464222052457</v>
       </c>
       <c r="X26" t="n">
-        <v>24.95</v>
+        <v>24.4327225851272</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.279310344827586</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>25.1464222052457</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>24.4327225851272</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3666,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
@@ -3675,18 +3468,9 @@
         <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN26" t="n">
         <v>148</v>
       </c>
     </row>
@@ -3703,85 +3487,85 @@
         <v>82.3721565961924</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>29.757785467128</v>
       </c>
       <c r="E27" t="n">
-        <v>29.757785467128</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="I27" t="n">
-        <v>177</v>
+        <v>81</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>512</v>
       </c>
       <c r="K27" t="n">
-        <v>165</v>
+        <v>758</v>
       </c>
       <c r="L27" t="n">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="M27" t="n">
-        <v>512</v>
+        <v>15</v>
       </c>
       <c r="N27" t="n">
-        <v>758</v>
+        <v>28</v>
       </c>
       <c r="O27" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="P27" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="Q27" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>25.4</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>0.25</v>
       </c>
       <c r="W27" t="n">
-        <v>1</v>
+        <v>25.6238859180036</v>
       </c>
       <c r="X27" t="n">
-        <v>25.4</v>
+        <v>24.8459903311873</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.254295532646048</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>25.6238859180036</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>24.8459903311873</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3790,27 +3574,18 @@
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI27" t="n">
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>78</v>
-      </c>
-      <c r="AN27" t="n">
         <v>234</v>
       </c>
     </row>
@@ -3827,76 +3602,76 @@
         <v>89.999695794357</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>21.1167800453514</v>
       </c>
       <c r="E28" t="n">
-        <v>21.1167800453514</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G28" t="n">
         <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>60</v>
+        <v>663</v>
       </c>
       <c r="I28" t="n">
-        <v>7540</v>
+        <v>493</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>567</v>
       </c>
       <c r="K28" t="n">
-        <v>663</v>
+        <v>1723</v>
       </c>
       <c r="L28" t="n">
-        <v>493</v>
+        <v>165</v>
       </c>
       <c r="M28" t="n">
-        <v>567</v>
+        <v>26</v>
       </c>
       <c r="N28" t="n">
-        <v>1723</v>
+        <v>16</v>
       </c>
       <c r="O28" t="n">
-        <v>165</v>
+        <v>207</v>
       </c>
       <c r="P28" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Q28" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>207</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>22.65</v>
       </c>
       <c r="V28" t="n">
-        <v>20</v>
+        <v>0.22</v>
       </c>
       <c r="W28" t="n">
-        <v>1</v>
+        <v>23.332060096766</v>
       </c>
       <c r="X28" t="n">
-        <v>22.65</v>
+        <v>22.8163986665956</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.223529411764706</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>23.332060096766</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>22.8163986665956</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -3911,30 +3686,21 @@
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
         <v>130</v>
       </c>
-      <c r="AN28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3949,77 +3715,79 @@
         <v>84.06136968590771</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>26.5118040651432</v>
       </c>
       <c r="E29" t="n">
-        <v>26.5118040651432</v>
+        <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>39</v>
-      </c>
-      <c r="I29" t="inlineStr"/>
+        <v>234.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>499.1</v>
+      </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>193.1</v>
       </c>
       <c r="K29" t="n">
-        <v>234.8</v>
+        <v>927.0000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>499.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>193.1</v>
+        <v>19.9</v>
       </c>
       <c r="N29" t="n">
-        <v>927</v>
+        <v>52.4</v>
       </c>
       <c r="O29" t="n">
-        <v>71.09999999999999</v>
+        <v>143.4</v>
       </c>
       <c r="P29" t="n">
-        <v>19.9</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>52.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>143.4</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>32.2</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="W29" t="n">
-        <v>1</v>
+        <v>27.5337407690349</v>
       </c>
       <c r="X29" t="n">
-        <v>32.2</v>
+        <v>27.2758127501023</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.373737373737374</v>
+        <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>27.5337407690349</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>27.2758127501023</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4034,7 +3802,7 @@
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
@@ -4043,18 +3811,9 @@
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1</v>
+        <v>96</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN29" t="n">
         <v>248</v>
       </c>
     </row>
@@ -4071,37 +3830,37 @@
         <v>81.78048907394729</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>29.4029202445788</v>
       </c>
       <c r="E30" t="n">
-        <v>29.4029202445788</v>
+        <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>35</v>
+        <v>183.6</v>
       </c>
       <c r="I30" t="n">
-        <v>6500</v>
+        <v>81.5</v>
       </c>
       <c r="J30" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="K30" t="n">
-        <v>183.6</v>
+        <v>327.1</v>
       </c>
       <c r="L30" t="n">
-        <v>81.5</v>
+        <v>47.4</v>
       </c>
       <c r="M30" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>327.1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>47.4</v>
@@ -4113,34 +3872,34 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>47.4</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X30" t="n">
-        <v>23.4</v>
+        <v>23.123937311856</v>
       </c>
       <c r="Y30" t="n">
-        <v>0.285714285714286</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>23.8731856378915</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.123937311856</v>
+        <v>1</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4149,13 +3908,13 @@
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -4164,21 +3923,12 @@
         <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
         <v>108</v>
       </c>
-      <c r="AN30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4193,88 +3943,88 @@
         <v>87.2016259474738</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>24.8970602317341</v>
       </c>
       <c r="E31" t="n">
-        <v>24.8970602317341</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>40</v>
+        <v>559.9</v>
       </c>
       <c r="I31" t="n">
-        <v>7150</v>
+        <v>375.9</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>722.8</v>
       </c>
       <c r="K31" t="n">
-        <v>559.9</v>
+        <v>1658.6</v>
       </c>
       <c r="L31" t="n">
-        <v>375.9</v>
+        <v>4.6</v>
       </c>
       <c r="M31" t="n">
-        <v>722.8</v>
+        <v>59.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1658.6</v>
+        <v>48.2</v>
       </c>
       <c r="O31" t="n">
-        <v>4.6</v>
+        <v>112.1</v>
       </c>
       <c r="P31" t="n">
-        <v>59.3</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>48.2</v>
+        <v>11.5</v>
       </c>
       <c r="R31" t="n">
-        <v>112.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>20.3</v>
       </c>
       <c r="T31" t="n">
-        <v>11.5</v>
+        <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>8.800000000000001</v>
+        <v>28.7</v>
       </c>
       <c r="V31" t="n">
-        <v>20.3</v>
+        <v>0.18</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>28.3295136236313</v>
       </c>
       <c r="X31" t="n">
-        <v>28.7</v>
+        <v>28.0261353964129</v>
       </c>
       <c r="Y31" t="n">
-        <v>0.183544303797468</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>28.3295136236313</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>28.0261353964129</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4289,22 +4039,13 @@
         <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
         <v>144</v>
       </c>
-      <c r="AN31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1820</v>
+        <v>572</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4312,83 +4053,85 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>82.0159771021877</v>
+        <v>84.1268081222907</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>25.3333333333333</v>
       </c>
       <c r="E32" t="n">
-        <v>22.65625</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H32" t="n">
-        <v>60</v>
-      </c>
-      <c r="I32" t="inlineStr"/>
+        <v>152</v>
+      </c>
+      <c r="I32" t="n">
+        <v>74</v>
+      </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="K32" t="n">
-        <v>278.1</v>
+        <v>301</v>
       </c>
       <c r="L32" t="n">
-        <v>44.3</v>
+        <v>67</v>
       </c>
       <c r="M32" t="n">
-        <v>68.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>391</v>
+        <v>6.5</v>
       </c>
       <c r="O32" t="n">
-        <v>35.8</v>
+        <v>73.5</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>35.8</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>21.4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W32" t="n">
-        <v>2</v>
+        <v>21.0084033613445</v>
       </c>
       <c r="X32" t="n">
-        <v>24.35</v>
+        <v>20.587687113627</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.266903914590747</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>24.4779730073848</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>23.8020432345551</v>
+        <v>1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4400,28 +4143,19 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>84</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>236</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33">
@@ -4437,79 +4171,79 @@
         <v>79.3961917256065</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>23.4567901234567</v>
       </c>
       <c r="E33" t="n">
-        <v>23.4567901234567</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H33" t="n">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="I33" t="n">
-        <v>1810</v>
+        <v>386</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>356</v>
       </c>
       <c r="K33" t="n">
-        <v>161</v>
+        <v>903</v>
       </c>
       <c r="L33" t="n">
-        <v>386</v>
+        <v>16</v>
       </c>
       <c r="M33" t="n">
-        <v>356</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>903</v>
+        <v>21</v>
       </c>
       <c r="O33" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="S33" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>18</v>
+        <v>27.05</v>
       </c>
       <c r="V33" t="n">
-        <v>32</v>
+        <v>0.2</v>
       </c>
       <c r="W33" t="n">
-        <v>1</v>
+        <v>27.3745861981156</v>
       </c>
       <c r="X33" t="n">
-        <v>27.05</v>
+        <v>26.8643892810307</v>
       </c>
       <c r="Y33" t="n">
-        <v>0.196666666666667</v>
+        <v>1</v>
       </c>
       <c r="Z33" t="n">
-        <v>27.3745861981156</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>26.8643892810307</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4518,7 +4252,7 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4533,18 +4267,9 @@
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="AK33" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN33" t="n">
         <v>152</v>
       </c>
     </row>
@@ -4561,76 +4286,76 @@
         <v>80.3077027086977</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>30.4498269896193</v>
       </c>
       <c r="E34" t="n">
-        <v>30.4498269896193</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>60</v>
+        <v>598</v>
       </c>
       <c r="I34" t="n">
-        <v>2000</v>
+        <v>182</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="K34" t="n">
-        <v>598</v>
+        <v>905</v>
       </c>
       <c r="L34" t="n">
-        <v>182</v>
+        <v>28</v>
       </c>
       <c r="M34" t="n">
-        <v>125</v>
+        <v>24</v>
       </c>
       <c r="N34" t="n">
-        <v>905</v>
+        <v>23</v>
       </c>
       <c r="O34" t="n">
-        <v>28</v>
+        <v>75</v>
       </c>
       <c r="P34" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" t="n">
-        <v>7</v>
+        <v>21.25</v>
       </c>
       <c r="V34" t="n">
-        <v>7</v>
+        <v>0.25</v>
       </c>
       <c r="W34" t="n">
-        <v>1</v>
+        <v>24.8281130634072</v>
       </c>
       <c r="X34" t="n">
-        <v>21.25</v>
+        <v>21.1668764239013</v>
       </c>
       <c r="Y34" t="n">
-        <v>0.251028806584362</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>24.8281130634072</v>
+        <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>21.1668764239013</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
@@ -4645,30 +4370,21 @@
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
         <v>100</v>
       </c>
-      <c r="AN34" t="inlineStr"/>
+      <c r="AK34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4683,86 +4399,88 @@
         <v>78.12271345095949</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>33.082612902219</v>
       </c>
       <c r="E35" t="n">
-        <v>33.082612902219</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G35" t="n">
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>35</v>
-      </c>
-      <c r="I35" t="inlineStr"/>
+        <v>369</v>
+      </c>
+      <c r="I35" t="n">
+        <v>330</v>
+      </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>267</v>
       </c>
       <c r="K35" t="n">
-        <v>369</v>
+        <v>966</v>
       </c>
       <c r="L35" t="n">
-        <v>330</v>
+        <v>14</v>
       </c>
       <c r="M35" t="n">
-        <v>267</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>966</v>
+        <v>43</v>
       </c>
       <c r="O35" t="n">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>26.25</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>26.7379679144385</v>
       </c>
       <c r="X35" t="n">
-        <v>26.25</v>
+        <v>26.2412231935231</v>
       </c>
       <c r="Y35" t="n">
-        <v>0.26158940397351</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>26.7379679144385</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>26.2412231935231</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -4777,24 +4495,15 @@
         <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>102</v>
-      </c>
-      <c r="AN35" t="n">
         <v>186</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>595</v>
+        <v>2746</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4802,82 +4511,82 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>82.8211651076127</v>
+        <v>84.10215399776919</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>21.4902855137932</v>
       </c>
       <c r="E36" t="n">
-        <v>27.5482093663911</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G36" t="n">
         <v>1</v>
       </c>
       <c r="H36" t="n">
+        <v>65</v>
+      </c>
+      <c r="I36" t="n">
         <v>60</v>
       </c>
-      <c r="I36" t="n">
-        <v>708</v>
-      </c>
       <c r="J36" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K36" t="n">
-        <v>397</v>
+        <v>175</v>
       </c>
       <c r="L36" t="n">
-        <v>456</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1082</v>
+        <v>20</v>
       </c>
       <c r="O36" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>22.75</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W36" t="n">
-        <v>2</v>
+        <v>22.7272727272727</v>
       </c>
       <c r="X36" t="n">
-        <v>23.75</v>
+        <v>22.0994437339948</v>
       </c>
       <c r="Y36" t="n">
-        <v>0.234200743494424</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>24.1914947797301</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>23.8260951566085</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -4889,10 +4598,10 @@
         <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
@@ -4901,24 +4610,13 @@
         <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>190</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="AK36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1662</v>
+        <v>548</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4926,88 +4624,88 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>83.6203661875428</v>
+        <v>81.8163586584531</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>17.8145087235996</v>
       </c>
       <c r="E37" t="n">
-        <v>24.0054869684499</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G37" t="n">
         <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="I37" t="n">
-        <v>2980</v>
+        <v>165</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="K37" t="n">
-        <v>111</v>
+        <v>646</v>
       </c>
       <c r="L37" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="M37" t="n">
-        <v>464</v>
+        <v>7</v>
       </c>
       <c r="N37" t="n">
-        <v>627</v>
+        <v>40</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P37" t="n">
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>23.55</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W37" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X37" t="n">
-        <v>23.95</v>
+        <v>23.5844721732425</v>
       </c>
       <c r="Y37" t="n">
-        <v>0.232472324723247</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>23.554876496053</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>23.3130652972889</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE37" t="n">
         <v>0</v>
@@ -5016,31 +4714,24 @@
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN37" t="inlineStr"/>
+        <v>192</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>548</v>
+        <v>2683</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -5048,83 +4739,85 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>81.8163586584531</v>
+        <v>84.3759558711689</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>29.9687825182101</v>
       </c>
       <c r="E38" t="n">
-        <v>17.8145087235996</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>60</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
+        <v>302</v>
+      </c>
+      <c r="I38" t="n">
+        <v>228</v>
+      </c>
       <c r="J38" t="n">
-        <v>1</v>
+        <v>176</v>
       </c>
       <c r="K38" t="n">
-        <v>370</v>
+        <v>706</v>
       </c>
       <c r="L38" t="n">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="M38" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>646</v>
+        <v>85</v>
       </c>
       <c r="O38" t="n">
-        <v>38</v>
+        <v>204</v>
       </c>
       <c r="P38" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
-        <v>29</v>
+        <v>22.4</v>
       </c>
       <c r="V38" t="n">
-        <v>29</v>
+        <v>0.25</v>
       </c>
       <c r="W38" t="n">
-        <v>2</v>
+        <v>23.1729055258467</v>
       </c>
       <c r="X38" t="n">
-        <v>23.55</v>
+        <v>22.4905136383469</v>
       </c>
       <c r="Y38" t="n">
-        <v>0.167315175097276</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="n">
-        <v>23.8731856378915</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>23.5844721732425</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5136,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
@@ -5145,24 +4838,15 @@
         <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="AK38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>70</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>192</v>
+        <v>133</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>315</v>
+        <v>594</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -5170,77 +4854,79 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>91.9351796397698</v>
+        <v>84.1788995360864</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>26.5731292517006</v>
       </c>
       <c r="E39" t="n">
-        <v>21.0961905148281</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>35</v>
-      </c>
-      <c r="I39" t="inlineStr"/>
+        <v>983</v>
+      </c>
+      <c r="I39" t="n">
+        <v>431</v>
+      </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>252</v>
       </c>
       <c r="K39" t="n">
-        <v>160</v>
+        <v>1666</v>
       </c>
       <c r="L39" t="n">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="M39" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="N39" t="n">
-        <v>362</v>
+        <v>63</v>
       </c>
       <c r="O39" t="n">
-        <v>29</v>
+        <v>274</v>
       </c>
       <c r="P39" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="Q39" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>14</v>
+        <v>21.55</v>
       </c>
       <c r="V39" t="n">
-        <v>14</v>
+        <v>0.2</v>
       </c>
       <c r="W39" t="n">
-        <v>2</v>
+        <v>21.6450216450216</v>
       </c>
       <c r="X39" t="n">
-        <v>20</v>
+        <v>20.9553534365411</v>
       </c>
       <c r="Y39" t="n">
-        <v>0.253275109170306</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>20.0534759358289</v>
+        <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>19.7354101179748</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -5255,36 +4941,27 @@
         <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>152</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>187</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>699</v>
+        <v>315</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -5292,77 +4969,79 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>85.002977412731</v>
+        <v>91.9351796397698</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>21.0961905148281</v>
       </c>
       <c r="E40" t="n">
-        <v>27.5482093663911</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>30</v>
-      </c>
-      <c r="I40" t="inlineStr"/>
+        <v>160</v>
+      </c>
+      <c r="I40" t="n">
+        <v>156</v>
+      </c>
       <c r="J40" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="K40" t="n">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="L40" t="n">
-        <v>396</v>
+        <v>29</v>
       </c>
       <c r="M40" t="n">
-        <v>385</v>
+        <v>32</v>
       </c>
       <c r="N40" t="n">
-        <v>1105</v>
+        <v>12</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="P40" t="n">
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>92</v>
+        <v>14</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W40" t="n">
-        <v>2</v>
+        <v>20.0534759358289</v>
       </c>
       <c r="X40" t="n">
-        <v>23.15</v>
+        <v>19.7354101179748</v>
       </c>
       <c r="Y40" t="n">
-        <v>0.31021897810219</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>23.554876496053</v>
+        <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>22.507485478497</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -5380,28 +5059,19 @@
         <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI40" t="n">
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="AK40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>164</v>
+        <v>187</v>
       </c>
     </row>
     <row r="41">
@@ -5417,85 +5087,85 @@
         <v>88.5210750500672</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>22.58955143605</v>
       </c>
       <c r="E41" t="n">
-        <v>22.58955143605</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="I41" t="n">
-        <v>351</v>
+        <v>209</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>242</v>
       </c>
       <c r="K41" t="n">
-        <v>77</v>
+        <v>528</v>
       </c>
       <c r="L41" t="n">
-        <v>209</v>
+        <v>15</v>
       </c>
       <c r="M41" t="n">
-        <v>242</v>
+        <v>99</v>
       </c>
       <c r="N41" t="n">
-        <v>528</v>
+        <v>116</v>
       </c>
       <c r="O41" t="n">
-        <v>15</v>
+        <v>230</v>
       </c>
       <c r="P41" t="n">
-        <v>99</v>
+        <v>48</v>
       </c>
       <c r="Q41" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="R41" t="n">
-        <v>230</v>
+        <v>249</v>
       </c>
       <c r="S41" t="n">
-        <v>48</v>
+        <v>419</v>
       </c>
       <c r="T41" t="n">
-        <v>122</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>249</v>
+        <v>24.85</v>
       </c>
       <c r="V41" t="n">
-        <v>419</v>
+        <v>0.18</v>
       </c>
       <c r="W41" t="n">
-        <v>1</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X41" t="n">
-        <v>24.85</v>
+        <v>23.9592772737234</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.17948717948718</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>24.1914947797301</v>
+        <v>1</v>
       </c>
       <c r="AA41" t="n">
-        <v>23.9592772737234</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
         <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE41" t="n">
         <v>0</v>
@@ -5504,33 +5174,24 @@
         <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI41" t="n">
         <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AK41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN41" t="n">
         <v>210</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>633</v>
+        <v>502</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -5538,79 +5199,79 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>82.8868868355008</v>
+        <v>85.2440515755317</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>21.3333333333333</v>
       </c>
       <c r="E42" t="n">
-        <v>37.4213957794838</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="n">
-        <v>30</v>
+        <v>166</v>
       </c>
       <c r="I42" t="n">
-        <v>7850</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="K42" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="L42" t="n">
-        <v>63.9</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
-        <v>165.6</v>
+        <v>5</v>
       </c>
       <c r="N42" t="n">
-        <v>416.5</v>
+        <v>8</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>20.3</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W42" t="n">
-        <v>2</v>
+        <v>20.3717850776674</v>
       </c>
       <c r="X42" t="n">
-        <v>24.8</v>
+        <v>20.1186577456453</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.222222222222222</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>25.305576776165</v>
+        <v>1</v>
       </c>
       <c r="AA42" t="n">
-        <v>24.856233988737</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
         <v>0</v>
@@ -5631,30 +5292,21 @@
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>138</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>136</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>236</v>
+        <v>150</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>587</v>
+        <v>663</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -5662,79 +5314,79 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>79.70262377367099</v>
+        <v>77.8163909803027</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>28.0403781445281</v>
       </c>
       <c r="E43" t="n">
-        <v>36.7309458218549</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>60</v>
+        <v>286</v>
       </c>
       <c r="I43" t="n">
-        <v>874</v>
+        <v>417</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>251</v>
       </c>
       <c r="K43" t="n">
-        <v>850</v>
+        <v>954</v>
       </c>
       <c r="L43" t="n">
-        <v>538</v>
+        <v>64</v>
       </c>
       <c r="M43" t="n">
-        <v>801</v>
+        <v>54</v>
       </c>
       <c r="N43" t="n">
-        <v>2189</v>
+        <v>31</v>
       </c>
       <c r="O43" t="n">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="P43" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Q43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="R43" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>21.7</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W43" t="n">
-        <v>1</v>
+        <v>21.6450216450216</v>
       </c>
       <c r="X43" t="n">
-        <v>23.75</v>
+        <v>21.3763064498772</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.26007326007326</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>23.554876496053</v>
+        <v>1</v>
       </c>
       <c r="AA43" t="n">
-        <v>22.8721164508225</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
         <v>0</v>
@@ -5749,36 +5401,27 @@
         <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI43" t="n">
         <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK43" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -5786,82 +5429,82 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>87.1852574340254</v>
+        <v>87.9164689329987</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>23.828125</v>
       </c>
       <c r="E44" t="n">
-        <v>21.6412742382271</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>35</v>
+        <v>529.7</v>
       </c>
       <c r="I44" t="n">
-        <v>6480</v>
+        <v>227.2</v>
       </c>
       <c r="J44" t="n">
-        <v>1</v>
+        <v>215.7</v>
       </c>
       <c r="K44" t="n">
-        <v>96.40000000000001</v>
+        <v>972.6000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>77.2</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>124.9</v>
+        <v>39.4</v>
       </c>
       <c r="N44" t="n">
-        <v>298.5</v>
+        <v>42.5</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="P44" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>50.6</v>
+        <v>6.5</v>
       </c>
       <c r="R44" t="n">
-        <v>58.3</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>64.7</v>
+        <v>23.7</v>
       </c>
       <c r="V44" t="n">
-        <v>64.7</v>
+        <v>0.2</v>
       </c>
       <c r="W44" t="n">
-        <v>2</v>
+        <v>23.9050165520754</v>
       </c>
       <c r="X44" t="n">
-        <v>20.25</v>
+        <v>23.6437635921209</v>
       </c>
       <c r="Y44" t="n">
-        <v>0.223684210526316</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>20.3081232492997</v>
+        <v>1</v>
       </c>
       <c r="AA44" t="n">
-        <v>20.0267116219144</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -5885,24 +5528,15 @@
         <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>114</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>138</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -5910,79 +5544,79 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>87.9164689329987</v>
+        <v>83.6477070499658</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>27.0551508844953</v>
       </c>
       <c r="E45" t="n">
-        <v>23.828125</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H45" t="n">
-        <v>60</v>
+        <v>214.2</v>
       </c>
       <c r="I45" t="n">
-        <v>8440</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>171.3</v>
       </c>
       <c r="K45" t="n">
-        <v>529.7</v>
+        <v>463.9</v>
       </c>
       <c r="L45" t="n">
-        <v>227.2</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>215.7</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>972.6</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="P45" t="n">
-        <v>39.4</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>42.5</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>81.90000000000001</v>
+        <v>29.8</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>29.8</v>
       </c>
       <c r="T45" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>20.75</v>
       </c>
       <c r="V45" t="n">
-        <v>6.5</v>
+        <v>0.13</v>
       </c>
       <c r="W45" t="n">
-        <v>2</v>
+        <v>20.6582633053221</v>
       </c>
       <c r="X45" t="n">
-        <v>23.7</v>
+        <v>20.4916344713353</v>
       </c>
       <c r="Y45" t="n">
-        <v>0.197718631178707</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="n">
-        <v>23.9050165520754</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>23.6437635921209</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -6006,27 +5640,16 @@
         <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>132</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>156</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="AK45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1584</v>
+        <v>1738</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -6034,79 +5657,79 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>90.1227350305473</v>
+        <v>83.02074935990061</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>25.9094569517874</v>
       </c>
       <c r="E46" t="n">
-        <v>32.8947368421052</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G46" t="n">
         <v>1</v>
       </c>
       <c r="H46" t="n">
-        <v>45</v>
+        <v>348</v>
       </c>
       <c r="I46" t="n">
-        <v>10400</v>
+        <v>223</v>
       </c>
       <c r="J46" t="n">
-        <v>1</v>
+        <v>290.6</v>
       </c>
       <c r="K46" t="n">
-        <v>132.7</v>
+        <v>861.6</v>
       </c>
       <c r="L46" t="n">
-        <v>101.7</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>107.1</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>341.5</v>
+        <v>121.2</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>194.6</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>30.2</v>
       </c>
       <c r="R46" t="n">
-        <v>5</v>
+        <v>143.4</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>173.6</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="W46" t="n">
-        <v>2</v>
+        <v>25.4647313470843</v>
       </c>
       <c r="X46" t="n">
-        <v>21.95</v>
+        <v>24.9482376369829</v>
       </c>
       <c r="Y46" t="n">
-        <v>0.27843137254902</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>23.1410746116628</v>
+        <v>1</v>
       </c>
       <c r="AA46" t="n">
-        <v>21.9926337013585</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
@@ -6121,36 +5744,27 @@
         <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI46" t="n">
         <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>152</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1677</v>
+        <v>696</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -6158,83 +5772,85 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>82.4924465738839</v>
+        <v>78.7061113329277</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>28.1969212010364</v>
       </c>
       <c r="E47" t="n">
-        <v>29.3333333333333</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47" t="n">
-        <v>60</v>
-      </c>
-      <c r="I47" t="inlineStr"/>
+        <v>842.5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>476.1</v>
+      </c>
       <c r="J47" t="n">
-        <v>1</v>
+        <v>627.6</v>
       </c>
       <c r="K47" t="n">
-        <v>112</v>
+        <v>1946.2</v>
       </c>
       <c r="L47" t="n">
-        <v>67</v>
+        <v>110.9</v>
       </c>
       <c r="M47" t="n">
-        <v>59</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="N47" t="n">
-        <v>238</v>
+        <v>219.1</v>
       </c>
       <c r="O47" t="n">
-        <v>25</v>
+        <v>409.9</v>
       </c>
       <c r="P47" t="n">
-        <v>9</v>
+        <v>39.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>46</v>
+        <v>57.7</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>15</v>
+        <v>24.3</v>
       </c>
       <c r="V47" t="n">
-        <v>15</v>
+        <v>0.21</v>
       </c>
       <c r="W47" t="n">
-        <v>2</v>
+        <v>24.2551566080978</v>
       </c>
       <c r="X47" t="n">
-        <v>21.8</v>
+        <v>23.9911309690755</v>
       </c>
       <c r="Y47" t="n">
-        <v>0.152542372881356</v>
+        <v>1</v>
       </c>
       <c r="Z47" t="n">
-        <v>21.9633307868602</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>21.7013276779863</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6243,7 +5859,7 @@
         <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -6255,19 +5871,10 @@
         <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM47" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN47" t="n">
-        <v>218</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48">
@@ -6283,79 +5890,79 @@
         <v>74.4324093086927</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>28.0898876404494</v>
       </c>
       <c r="E48" t="n">
-        <v>28.0898876404494</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G48" t="n">
         <v>1</v>
       </c>
       <c r="H48" t="n">
-        <v>55</v>
+        <v>513.6</v>
       </c>
       <c r="I48" t="n">
-        <v>1190</v>
+        <v>246.7</v>
       </c>
       <c r="J48" t="n">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="K48" t="n">
-        <v>513.6</v>
+        <v>913.3</v>
       </c>
       <c r="L48" t="n">
-        <v>246.7</v>
+        <v>136.5</v>
       </c>
       <c r="M48" t="n">
-        <v>153</v>
+        <v>40.9</v>
       </c>
       <c r="N48" t="n">
-        <v>913.3</v>
+        <v>6.5</v>
       </c>
       <c r="O48" t="n">
-        <v>136.5</v>
+        <v>183.9</v>
       </c>
       <c r="P48" t="n">
-        <v>40.9</v>
+        <v>88</v>
       </c>
       <c r="Q48" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>183.9</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>88</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V48" t="n">
-        <v>88</v>
+        <v>0.15</v>
       </c>
       <c r="W48" t="n">
-        <v>1</v>
+        <v>25.305576776165</v>
       </c>
       <c r="X48" t="n">
-        <v>25</v>
+        <v>25.1135016550657</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.148148148148148</v>
+        <v>1</v>
       </c>
       <c r="Z48" t="n">
-        <v>25.305576776165</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>25.1135016550657</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
         <v>0</v>
@@ -6367,7 +5974,7 @@
         <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -6376,21 +5983,12 @@
         <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
         <v>82</v>
       </c>
-      <c r="AN48" t="inlineStr"/>
+      <c r="AK48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6405,74 +6003,76 @@
         <v>86.20518711815851</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>29.4022732977159</v>
       </c>
       <c r="E49" t="n">
-        <v>29.4022732977159</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>60</v>
-      </c>
-      <c r="I49" t="inlineStr"/>
+        <v>341</v>
+      </c>
+      <c r="I49" t="n">
+        <v>334</v>
+      </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>371</v>
       </c>
       <c r="K49" t="n">
-        <v>341</v>
+        <v>1046</v>
       </c>
       <c r="L49" t="n">
-        <v>334</v>
+        <v>96</v>
       </c>
       <c r="M49" t="n">
-        <v>371</v>
+        <v>17</v>
       </c>
       <c r="N49" t="n">
-        <v>1046</v>
+        <v>194</v>
       </c>
       <c r="O49" t="n">
-        <v>96</v>
+        <v>307</v>
       </c>
       <c r="P49" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>307</v>
+        <v>10</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>10</v>
+        <v>21.6</v>
       </c>
       <c r="V49" t="n">
-        <v>10</v>
+        <v>0.31</v>
       </c>
       <c r="W49" t="n">
-        <v>2</v>
+        <v>22.2816399286988</v>
       </c>
       <c r="X49" t="n">
-        <v>21.6</v>
+        <v>21.2269244209251</v>
       </c>
       <c r="Y49" t="n">
-        <v>0.3125</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>22.2816399286988</v>
+        <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>21.2269244209251</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
         <v>0</v>
@@ -6487,30 +6087,21 @@
         <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN49" t="n">
         <v>204</v>
       </c>
     </row>
@@ -6527,86 +6118,88 @@
         <v>78.1972106877583</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>27.0416441319632</v>
       </c>
       <c r="E50" t="n">
-        <v>27.0416441319632</v>
+        <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>60</v>
-      </c>
-      <c r="I50" t="inlineStr"/>
+        <v>288</v>
+      </c>
+      <c r="I50" t="n">
+        <v>282</v>
+      </c>
       <c r="J50" t="n">
-        <v>1</v>
+        <v>418</v>
       </c>
       <c r="K50" t="n">
-        <v>288</v>
+        <v>988</v>
       </c>
       <c r="L50" t="n">
-        <v>282</v>
+        <v>47</v>
       </c>
       <c r="M50" t="n">
-        <v>418</v>
+        <v>28</v>
       </c>
       <c r="N50" t="n">
-        <v>988</v>
+        <v>166</v>
       </c>
       <c r="O50" t="n">
-        <v>47</v>
+        <v>241</v>
       </c>
       <c r="P50" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>241</v>
+        <v>76</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>76</v>
+        <v>25.9</v>
       </c>
       <c r="V50" t="n">
-        <v>76</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="W50" t="n">
-        <v>1</v>
+        <v>26.2605042016807</v>
       </c>
       <c r="X50" t="n">
-        <v>25.9</v>
+        <v>25.8502706383632</v>
       </c>
       <c r="Y50" t="n">
-        <v>0.0743494423791822</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>26.2605042016807</v>
+        <v>1</v>
       </c>
       <c r="AA50" t="n">
-        <v>25.8502706383632</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -6621,22 +6214,13 @@
         <v>0</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM50" t="n">
         <v>138</v>
       </c>
-      <c r="AN50" t="inlineStr"/>
+      <c r="AK50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>571</v>
+        <v>1331</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -6644,82 +6228,82 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>78.9525439196897</v>
+        <v>77.67647340101909</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>20.7612456747404</v>
       </c>
       <c r="E51" t="n">
-        <v>25.2493372048983</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>28</v>
+        <v>296</v>
       </c>
       <c r="I51" t="n">
-        <v>7730</v>
+        <v>221</v>
       </c>
       <c r="J51" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="K51" t="n">
-        <v>650</v>
+        <v>555</v>
       </c>
       <c r="L51" t="n">
-        <v>852</v>
+        <v>8</v>
       </c>
       <c r="M51" t="n">
-        <v>646</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>2148</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="P51" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>314</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U51" t="n">
-        <v>157</v>
+        <v>21.85</v>
       </c>
       <c r="V51" t="n">
-        <v>168</v>
+        <v>0.24</v>
       </c>
       <c r="W51" t="n">
-        <v>1</v>
+        <v>21.9633307868602</v>
       </c>
       <c r="X51" t="n">
-        <v>27.35</v>
+        <v>21.4654366757236</v>
       </c>
       <c r="Y51" t="n">
-        <v>0.285266457680251</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>27.7565571683219</v>
+        <v>1</v>
       </c>
       <c r="AA51" t="n">
-        <v>27.0297101600648</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
         <v>0</v>
@@ -6731,30 +6315,23 @@
         <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="AK51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN51" t="inlineStr"/>
+        <v>180</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6769,82 +6346,82 @@
         <v>80.58966781377541</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>24.0185950413223</v>
       </c>
       <c r="E52" t="n">
-        <v>24.0185950413223</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G52" t="n">
         <v>1</v>
       </c>
       <c r="H52" t="n">
-        <v>60</v>
+        <v>300.2</v>
       </c>
       <c r="I52" t="n">
-        <v>3820</v>
+        <v>160.2</v>
       </c>
       <c r="J52" t="n">
-        <v>1</v>
+        <v>237.9</v>
       </c>
       <c r="K52" t="n">
-        <v>300.2</v>
+        <v>698.3</v>
       </c>
       <c r="L52" t="n">
-        <v>160.2</v>
+        <v>29.4</v>
       </c>
       <c r="M52" t="n">
-        <v>237.9</v>
+        <v>5.4</v>
       </c>
       <c r="N52" t="n">
-        <v>698.3</v>
+        <v>10.7</v>
       </c>
       <c r="O52" t="n">
-        <v>29.4</v>
+        <v>45.5</v>
       </c>
       <c r="P52" t="n">
-        <v>5.4</v>
+        <v>4.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>10.7</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>45.5</v>
+        <v>21.4</v>
       </c>
       <c r="S52" t="n">
-        <v>4.2</v>
+        <v>25.6</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U52" t="n">
-        <v>21.4</v>
+        <v>22.85</v>
       </c>
       <c r="V52" t="n">
-        <v>25.6</v>
+        <v>0.19</v>
       </c>
       <c r="W52" t="n">
-        <v>1</v>
+        <v>22.7909345556404</v>
       </c>
       <c r="X52" t="n">
-        <v>22.85</v>
+        <v>22.4650318371583</v>
       </c>
       <c r="Y52" t="n">
-        <v>0.193675889328063</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>22.7909345556404</v>
+        <v>1</v>
       </c>
       <c r="AA52" t="n">
-        <v>22.4650318371583</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
         <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
         <v>0</v>
@@ -6853,7 +6430,7 @@
         <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -6862,25 +6439,16 @@
         <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
         <v>82</v>
       </c>
-      <c r="AN52" t="inlineStr"/>
+      <c r="AK52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -6888,85 +6456,85 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>79.51356757167849</v>
+        <v>88.7510476081831</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>20.9366391184573</v>
       </c>
       <c r="E53" t="n">
-        <v>21.09375</v>
+        <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G53" t="n">
         <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>20</v>
+        <v>217</v>
       </c>
       <c r="I53" t="n">
-        <v>35000</v>
+        <v>55</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>132</v>
       </c>
       <c r="K53" t="n">
-        <v>523</v>
+        <v>404</v>
       </c>
       <c r="L53" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>279</v>
+        <v>14</v>
       </c>
       <c r="N53" t="n">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="P53" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="W53" t="n">
-        <v>2</v>
+        <v>22.440794499618</v>
       </c>
       <c r="X53" t="n">
-        <v>23.9</v>
+        <v>21.7599008686688</v>
       </c>
       <c r="Y53" t="n">
-        <v>0.223048327137547</v>
+        <v>1</v>
       </c>
       <c r="Z53" t="n">
-        <v>23.8731856378915</v>
+        <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>23.5844721732425</v>
+        <v>0</v>
       </c>
       <c r="AB53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD53" t="n">
         <v>0</v>
@@ -6978,27 +6546,18 @@
         <v>0</v>
       </c>
       <c r="AG53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN53" t="inlineStr"/>
+        <v>146</v>
+      </c>
+      <c r="AK53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7013,76 +6572,76 @@
         <v>81.5532471734226</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>22.1453287197231</v>
       </c>
       <c r="E54" t="n">
-        <v>22.1453287197231</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" t="n">
-        <v>38</v>
+        <v>299</v>
       </c>
       <c r="I54" t="n">
-        <v>4090</v>
+        <v>129</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="K54" t="n">
-        <v>299</v>
+        <v>508</v>
       </c>
       <c r="L54" t="n">
-        <v>129</v>
+        <v>86</v>
       </c>
       <c r="M54" t="n">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="N54" t="n">
-        <v>508</v>
+        <v>26</v>
       </c>
       <c r="O54" t="n">
-        <v>86</v>
+        <v>120</v>
       </c>
       <c r="P54" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="Q54" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>47</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>0</v>
+        <v>22.45</v>
       </c>
       <c r="V54" t="n">
-        <v>47</v>
+        <v>0.15</v>
       </c>
       <c r="W54" t="n">
-        <v>1</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X54" t="n">
-        <v>22.45</v>
+        <v>22.1655797488585</v>
       </c>
       <c r="Y54" t="n">
-        <v>0.152263374485597</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
-        <v>22.5999490705373</v>
+        <v>1</v>
       </c>
       <c r="AA54" t="n">
-        <v>22.1655797488585</v>
+        <v>0</v>
       </c>
       <c r="AB54" t="n">
         <v>0</v>
@@ -7097,36 +6656,27 @@
         <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI54" t="n">
         <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AK54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN54" t="n">
         <v>184</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>504</v>
+        <v>609</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -7134,79 +6684,79 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>90.94137209420241</v>
+        <v>88.2475587497148</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>22.8928199791883</v>
       </c>
       <c r="E55" t="n">
-        <v>20.9366391184573</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="G55" t="n">
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>46</v>
+        <v>590</v>
       </c>
       <c r="I55" t="n">
-        <v>12300</v>
+        <v>257</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>274</v>
       </c>
       <c r="K55" t="n">
-        <v>658</v>
+        <v>1121</v>
       </c>
       <c r="L55" t="n">
-        <v>344</v>
+        <v>87</v>
       </c>
       <c r="M55" t="n">
-        <v>432</v>
+        <v>21</v>
       </c>
       <c r="N55" t="n">
-        <v>1434</v>
+        <v>91</v>
       </c>
       <c r="O55" t="n">
-        <v>158</v>
+        <v>199</v>
       </c>
       <c r="P55" t="n">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="Q55" t="n">
-        <v>127</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>389</v>
+        <v>24</v>
       </c>
       <c r="S55" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="T55" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="U55" t="n">
-        <v>12</v>
+        <v>23.2</v>
       </c>
       <c r="V55" t="n">
-        <v>89</v>
+        <v>0.18</v>
       </c>
       <c r="W55" t="n">
-        <v>2</v>
+        <v>23.6822001527884</v>
       </c>
       <c r="X55" t="n">
-        <v>22.25</v>
+        <v>23.2584038731959</v>
       </c>
       <c r="Y55" t="n">
-        <v>0.327067669172932</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>22.5999490705373</v>
+        <v>1</v>
       </c>
       <c r="AA55" t="n">
-        <v>21.7013276779863</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
         <v>0</v>
@@ -7221,31 +6771,22 @@
         <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="AK55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="56">
@@ -7261,112 +6802,105 @@
         <v>81.09328054097899</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>25.0995015956111</v>
       </c>
       <c r="E56" t="n">
-        <v>25.0995015956111</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
-        <v>50</v>
-      </c>
-      <c r="I56" t="inlineStr"/>
+        <v>611</v>
+      </c>
+      <c r="I56" t="n">
+        <v>156</v>
+      </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>141</v>
       </c>
       <c r="K56" t="n">
-        <v>611</v>
+        <v>908</v>
       </c>
       <c r="L56" t="n">
-        <v>156</v>
+        <v>188</v>
       </c>
       <c r="M56" t="n">
-        <v>141</v>
+        <v>11</v>
       </c>
       <c r="N56" t="n">
-        <v>908</v>
+        <v>10</v>
       </c>
       <c r="O56" t="n">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="P56" t="n">
-        <v>11</v>
+        <v>102</v>
       </c>
       <c r="Q56" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>209</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>102</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>27.8</v>
       </c>
       <c r="V56" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="W56" t="n">
+        <v>28.0112044817927</v>
+      </c>
+      <c r="X56" t="n">
+        <v>27.7270657254151</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="n">
         <v>102</v>
       </c>
-      <c r="W56" t="n">
-        <v>2</v>
-      </c>
-      <c r="X56" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="Y56" t="n">
-        <v>0.177049180327869</v>
-      </c>
-      <c r="Z56" t="n">
-        <v>28.0112044817927</v>
-      </c>
-      <c r="AA56" t="n">
-        <v>27.7270657254151</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>0</v>
-      </c>
       <c r="AK56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL56" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM56" t="n">
-        <v>102</v>
-      </c>
-      <c r="AN56" t="n">
         <v>150</v>
       </c>
     </row>
@@ -7383,76 +6917,76 @@
         <v>65.8248574036048</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>38.7543252595155</v>
       </c>
       <c r="E57" t="n">
-        <v>38.7543252595155</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G57" t="n">
         <v>1</v>
       </c>
       <c r="H57" t="n">
-        <v>12</v>
+        <v>511</v>
       </c>
       <c r="I57" t="n">
-        <v>11800</v>
+        <v>525</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>415</v>
       </c>
       <c r="K57" t="n">
-        <v>511</v>
+        <v>1451</v>
       </c>
       <c r="L57" t="n">
-        <v>525</v>
+        <v>98</v>
       </c>
       <c r="M57" t="n">
-        <v>415</v>
+        <v>50</v>
       </c>
       <c r="N57" t="n">
-        <v>1451</v>
+        <v>64</v>
       </c>
       <c r="O57" t="n">
-        <v>98</v>
+        <v>212</v>
       </c>
       <c r="P57" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>212</v>
+        <v>22</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U57" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="V57" t="n">
-        <v>22</v>
+        <v>0.24</v>
       </c>
       <c r="W57" t="n">
-        <v>1</v>
+        <v>31.0669722434428</v>
       </c>
       <c r="X57" t="n">
-        <v>31</v>
+        <v>30.5239675446498</v>
       </c>
       <c r="Y57" t="n">
-        <v>0.243626062322946</v>
+        <v>0</v>
       </c>
       <c r="Z57" t="n">
-        <v>31.0669722434428</v>
+        <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>30.5239675446498</v>
+        <v>1</v>
       </c>
       <c r="AB57" t="n">
         <v>0</v>
@@ -7461,10 +6995,10 @@
         <v>0</v>
       </c>
       <c r="AD57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF57" t="n">
         <v>0</v>
@@ -7479,18 +7013,9 @@
         <v>0</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL57" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM57" t="n">
         <v>110</v>
       </c>
-      <c r="AN57" t="inlineStr"/>
+      <c r="AK57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7505,76 +7030,76 @@
         <v>81.12338476309991</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>27.4405991735537</v>
       </c>
       <c r="E58" t="n">
-        <v>27.4405991735537</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="n">
-        <v>60</v>
+        <v>244</v>
       </c>
       <c r="I58" t="n">
-        <v>459</v>
+        <v>119</v>
       </c>
       <c r="J58" t="n">
-        <v>1</v>
+        <v>248</v>
       </c>
       <c r="K58" t="n">
-        <v>244</v>
+        <v>611</v>
       </c>
       <c r="L58" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>248</v>
+        <v>0</v>
       </c>
       <c r="N58" t="n">
-        <v>611</v>
+        <v>50</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="P58" t="n">
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
       </c>
       <c r="T58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>22.5</v>
       </c>
       <c r="V58" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W58" t="n">
-        <v>1</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X58" t="n">
-        <v>22.5</v>
+        <v>21.934681996673</v>
       </c>
       <c r="Y58" t="n">
-        <v>0.30188679245283</v>
+        <v>0</v>
       </c>
       <c r="Z58" t="n">
-        <v>22.5999490705373</v>
+        <v>1</v>
       </c>
       <c r="AA58" t="n">
-        <v>21.934681996673</v>
+        <v>0</v>
       </c>
       <c r="AB58" t="n">
         <v>0</v>
@@ -7589,30 +7114,21 @@
         <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL58" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM58" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN58" t="n">
         <v>160</v>
       </c>
     </row>
@@ -7629,76 +7145,76 @@
         <v>75.0920773442847</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>29.0547520661157</v>
       </c>
       <c r="E59" t="n">
-        <v>29.0547520661157</v>
+        <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G59" t="n">
         <v>1</v>
       </c>
       <c r="H59" t="n">
-        <v>60</v>
+        <v>761</v>
       </c>
       <c r="I59" t="n">
-        <v>1310</v>
+        <v>532</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>463</v>
       </c>
       <c r="K59" t="n">
-        <v>761</v>
+        <v>1756</v>
       </c>
       <c r="L59" t="n">
-        <v>532</v>
+        <v>212</v>
       </c>
       <c r="M59" t="n">
-        <v>463</v>
+        <v>245</v>
       </c>
       <c r="N59" t="n">
-        <v>1756</v>
+        <v>219</v>
       </c>
       <c r="O59" t="n">
-        <v>212</v>
+        <v>676</v>
       </c>
       <c r="P59" t="n">
-        <v>245</v>
+        <v>36</v>
       </c>
       <c r="Q59" t="n">
-        <v>219</v>
+        <v>145</v>
       </c>
       <c r="R59" t="n">
-        <v>676</v>
+        <v>201</v>
       </c>
       <c r="S59" t="n">
-        <v>36</v>
+        <v>382</v>
       </c>
       <c r="T59" t="n">
-        <v>145</v>
+        <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>201</v>
+        <v>28.95</v>
       </c>
       <c r="V59" t="n">
-        <v>382</v>
+        <v>0.16</v>
       </c>
       <c r="W59" t="n">
-        <v>1</v>
+        <v>29.6027501909855</v>
       </c>
       <c r="X59" t="n">
-        <v>28.95</v>
+        <v>28.5636996210264</v>
       </c>
       <c r="Y59" t="n">
-        <v>0.156050955414013</v>
+        <v>0</v>
       </c>
       <c r="Z59" t="n">
-        <v>29.6027501909855</v>
+        <v>0</v>
       </c>
       <c r="AA59" t="n">
-        <v>28.5636996210264</v>
+        <v>1</v>
       </c>
       <c r="AB59" t="n">
         <v>0</v>
@@ -7707,10 +7223,10 @@
         <v>0</v>
       </c>
       <c r="AD59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF59" t="n">
         <v>0</v>
@@ -7725,18 +7241,9 @@
         <v>0</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL59" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM59" t="n">
         <v>94</v>
       </c>
-      <c r="AN59" t="inlineStr"/>
+      <c r="AK59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7751,85 +7258,85 @@
         <v>83.2233268689634</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>24.5089457652042</v>
       </c>
       <c r="E60" t="n">
-        <v>24.5089457652042</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G60" t="n">
         <v>1</v>
       </c>
       <c r="H60" t="n">
-        <v>30</v>
+        <v>530</v>
       </c>
       <c r="I60" t="n">
-        <v>27000</v>
+        <v>397</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>501</v>
       </c>
       <c r="K60" t="n">
-        <v>530</v>
+        <v>1428</v>
       </c>
       <c r="L60" t="n">
-        <v>397</v>
+        <v>35</v>
       </c>
       <c r="M60" t="n">
-        <v>501</v>
+        <v>21</v>
       </c>
       <c r="N60" t="n">
-        <v>1428</v>
+        <v>143</v>
       </c>
       <c r="O60" t="n">
-        <v>35</v>
+        <v>199</v>
       </c>
       <c r="P60" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Q60" t="n">
-        <v>143</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>199</v>
+        <v>55</v>
       </c>
       <c r="S60" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="T60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U60" t="n">
-        <v>55</v>
+        <v>23.95</v>
       </c>
       <c r="V60" t="n">
-        <v>62</v>
+        <v>0.19</v>
       </c>
       <c r="W60" t="n">
-        <v>1</v>
+        <v>24.1914947797301</v>
       </c>
       <c r="X60" t="n">
-        <v>23.95</v>
+        <v>23.8260951566085</v>
       </c>
       <c r="Y60" t="n">
-        <v>0.192452830188679</v>
+        <v>1</v>
       </c>
       <c r="Z60" t="n">
-        <v>24.1914947797301</v>
+        <v>0</v>
       </c>
       <c r="AA60" t="n">
-        <v>23.8260951566085</v>
+        <v>0</v>
       </c>
       <c r="AB60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC60" t="n">
         <v>0</v>
       </c>
       <c r="AD60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE60" t="n">
         <v>0</v>
@@ -7838,33 +7345,24 @@
         <v>0</v>
       </c>
       <c r="AG60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="AK60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM60" t="n">
-        <v>86</v>
-      </c>
-      <c r="AN60" t="n">
         <v>160</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1738</v>
+        <v>667</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -7872,79 +7370,79 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>83.02074935990061</v>
+        <v>84.9569007148833</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>27.0551508844953</v>
       </c>
       <c r="E61" t="n">
-        <v>25.9094569517874</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="n">
-        <v>60</v>
+        <v>122.4</v>
       </c>
       <c r="I61" t="n">
-        <v>1650</v>
+        <v>112.1</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>504</v>
       </c>
       <c r="K61" t="n">
-        <v>348</v>
+        <v>738.5</v>
       </c>
       <c r="L61" t="n">
-        <v>223</v>
+        <v>6.5</v>
       </c>
       <c r="M61" t="n">
-        <v>290.6</v>
+        <v>35.9</v>
       </c>
       <c r="N61" t="n">
-        <v>861.6</v>
+        <v>99.8</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>142.2</v>
       </c>
       <c r="P61" t="n">
-        <v>73.40000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>121.2</v>
+        <v>7.6</v>
       </c>
       <c r="R61" t="n">
-        <v>194.6</v>
+        <v>85.3</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="T61" t="n">
-        <v>30.2</v>
+        <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>143.4</v>
+        <v>22.3</v>
       </c>
       <c r="V61" t="n">
-        <v>173.6</v>
+        <v>0.15</v>
       </c>
       <c r="W61" t="n">
-        <v>2</v>
+        <v>22.7591036414566</v>
       </c>
       <c r="X61" t="n">
-        <v>25.6</v>
+        <v>22.6146780197282</v>
       </c>
       <c r="Y61" t="n">
-        <v>0.23448275862069</v>
+        <v>0</v>
       </c>
       <c r="Z61" t="n">
-        <v>25.4647313470843</v>
+        <v>1</v>
       </c>
       <c r="AA61" t="n">
-        <v>24.9482376369829</v>
+        <v>0</v>
       </c>
       <c r="AB61" t="n">
         <v>0</v>
@@ -7962,7 +7460,7 @@
         <v>0</v>
       </c>
       <c r="AG61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH61" t="n">
         <v>0</v>
@@ -7971,19 +7469,10 @@
         <v>0</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="AK61" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>176</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62">
@@ -7999,85 +7488,85 @@
         <v>89.0552380409157</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>25.3086419753086</v>
       </c>
       <c r="E62" t="n">
-        <v>25.3086419753086</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="n">
-        <v>60</v>
+        <v>1053</v>
       </c>
       <c r="I62" t="n">
+        <v>429</v>
+      </c>
+      <c r="J62" t="n">
+        <v>678</v>
+      </c>
+      <c r="K62" t="n">
         <v>2160</v>
       </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="n">
-        <v>1053</v>
-      </c>
       <c r="L62" t="n">
-        <v>429</v>
+        <v>152</v>
       </c>
       <c r="M62" t="n">
-        <v>678</v>
+        <v>25</v>
       </c>
       <c r="N62" t="n">
-        <v>2160</v>
+        <v>235</v>
       </c>
       <c r="O62" t="n">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="P62" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="Q62" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>412</v>
+        <v>140</v>
       </c>
       <c r="S62" t="n">
-        <v>9</v>
+        <v>149</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U62" t="n">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="V62" t="n">
-        <v>149</v>
+        <v>0.18</v>
       </c>
       <c r="W62" t="n">
-        <v>1</v>
+        <v>25.7830404889228</v>
       </c>
       <c r="X62" t="n">
-        <v>26</v>
+        <v>25.5157454916499</v>
       </c>
       <c r="Y62" t="n">
-        <v>0.175438596491228</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>25.7830404889228</v>
+        <v>1</v>
       </c>
       <c r="AA62" t="n">
-        <v>25.5157454916499</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
         <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE62" t="n">
         <v>0</v>
@@ -8086,33 +7575,24 @@
         <v>0</v>
       </c>
       <c r="AG62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AK62" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL62" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM62" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN62" t="n">
         <v>160</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>572</v>
+        <v>504</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -8120,118 +7600,109 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>84.1268081222907</v>
+        <v>90.94137209420241</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>20.9366391184573</v>
       </c>
       <c r="E63" t="n">
-        <v>25.3333333333333</v>
+        <v>1</v>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="n">
-        <v>60</v>
+        <v>658</v>
       </c>
       <c r="I63" t="n">
-        <v>411</v>
+        <v>344</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>432</v>
       </c>
       <c r="K63" t="n">
-        <v>152</v>
+        <v>1434</v>
       </c>
       <c r="L63" t="n">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="M63" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="N63" t="n">
-        <v>301</v>
+        <v>127</v>
       </c>
       <c r="O63" t="n">
-        <v>67</v>
+        <v>389</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="Q63" t="n">
-        <v>6.5</v>
+        <v>46</v>
       </c>
       <c r="R63" t="n">
-        <v>73.5</v>
+        <v>12</v>
       </c>
       <c r="S63" t="n">
-        <v>46</v>
+        <v>89</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>22.25</v>
       </c>
       <c r="V63" t="n">
-        <v>46</v>
+        <v>0.33</v>
       </c>
       <c r="W63" t="n">
-        <v>2</v>
+        <v>22.5999490705373</v>
       </c>
       <c r="X63" t="n">
-        <v>21.4</v>
+        <v>21.7013276779863</v>
       </c>
       <c r="Y63" t="n">
-        <v>0.209205020920502</v>
+        <v>0</v>
       </c>
       <c r="Z63" t="n">
-        <v>21.0084033613445</v>
+        <v>1</v>
       </c>
       <c r="AA63" t="n">
-        <v>20.587687113627</v>
+        <v>0</v>
       </c>
       <c r="AB63" t="n">
         <v>0</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE63" t="n">
         <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI63" t="n">
         <v>0</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>244</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64">
@@ -8247,86 +7718,88 @@
         <v>80.90501932973361</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>37.5510204081632</v>
       </c>
       <c r="E64" t="n">
-        <v>37.5510204081632</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G64" t="n">
         <v>1</v>
       </c>
       <c r="H64" t="n">
-        <v>45</v>
-      </c>
-      <c r="I64" t="inlineStr"/>
+        <v>350.7</v>
+      </c>
+      <c r="I64" t="n">
+        <v>246.3</v>
+      </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>441.7</v>
       </c>
       <c r="K64" t="n">
-        <v>350.7</v>
+        <v>1038.7</v>
       </c>
       <c r="L64" t="n">
-        <v>246.3</v>
+        <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>441.7</v>
+        <v>16.4</v>
       </c>
       <c r="N64" t="n">
-        <v>1038.7</v>
+        <v>37.1</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>53.5</v>
       </c>
       <c r="P64" t="n">
-        <v>16.4</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>37.1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>53.5</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>29.95</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W64" t="n">
-        <v>1</v>
+        <v>29.8255665902725</v>
       </c>
       <c r="X64" t="n">
-        <v>29.95</v>
+        <v>29.3981722178852</v>
       </c>
       <c r="Y64" t="n">
-        <v>0.217261904761905</v>
+        <v>0</v>
       </c>
       <c r="Z64" t="n">
-        <v>29.8255665902725</v>
+        <v>1</v>
       </c>
       <c r="AA64" t="n">
-        <v>29.3981722178852</v>
+        <v>0</v>
       </c>
       <c r="AB64" t="n">
         <v>0</v>
       </c>
       <c r="AC64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD64" t="n">
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF64" t="n">
         <v>0</v>
@@ -8341,22 +7814,13 @@
         <v>0</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL64" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM64" t="n">
         <v>98</v>
       </c>
-      <c r="AN64" t="inlineStr"/>
+      <c r="AK64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>663</v>
+        <v>1820</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -8364,123 +7828,114 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>77.8163909803027</v>
+        <v>82.0159771021877</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>22.65625</v>
       </c>
       <c r="E65" t="n">
-        <v>28.0403781445281</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="n">
-        <v>60</v>
+        <v>278.1</v>
       </c>
       <c r="I65" t="n">
-        <v>1340</v>
+        <v>44.3</v>
       </c>
       <c r="J65" t="n">
-        <v>1</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>286</v>
+        <v>391</v>
       </c>
       <c r="L65" t="n">
-        <v>417</v>
+        <v>35.8</v>
       </c>
       <c r="M65" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="N65" t="n">
-        <v>954</v>
+        <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>64</v>
+        <v>35.8</v>
       </c>
       <c r="P65" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>24.35</v>
       </c>
       <c r="V65" t="n">
-        <v>24</v>
+        <v>0.27</v>
       </c>
       <c r="W65" t="n">
-        <v>2</v>
+        <v>24.4779730073848</v>
       </c>
       <c r="X65" t="n">
-        <v>21.7</v>
+        <v>23.8020432345551</v>
       </c>
       <c r="Y65" t="n">
-        <v>0.221311475409836</v>
+        <v>1</v>
       </c>
       <c r="Z65" t="n">
-        <v>21.6450216450216</v>
+        <v>0</v>
       </c>
       <c r="AA65" t="n">
-        <v>21.3763064498772</v>
+        <v>0</v>
       </c>
       <c r="AB65" t="n">
         <v>0</v>
       </c>
       <c r="AC65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE65" t="n">
         <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI65" t="n">
         <v>0</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AK65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL65" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM65" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN65" t="n">
-        <v>170</v>
+        <v>236</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1695</v>
+        <v>1387</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -8488,38 +7943,40 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>72.6859265913758</v>
+        <v>89.14018851243441</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>25.78125</v>
       </c>
       <c r="E66" t="n">
-        <v>26.0374939913475</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="n">
-        <v>60</v>
-      </c>
-      <c r="I66" t="inlineStr"/>
+        <v>46.3</v>
+      </c>
+      <c r="I66" t="n">
+        <v>42.8</v>
+      </c>
       <c r="J66" t="n">
-        <v>0</v>
+        <v>31.7</v>
       </c>
       <c r="K66" t="n">
-        <v>160.6</v>
+        <v>120.8</v>
       </c>
       <c r="L66" t="n">
-        <v>74.59999999999999</v>
+        <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>58.1</v>
+        <v>0</v>
       </c>
       <c r="N66" t="n">
-        <v>293.3</v>
+        <v>0</v>
       </c>
       <c r="O66" t="n">
         <v>0</v>
@@ -8528,37 +7985,37 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>13.4</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>11.1</v>
+        <v>0</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U66" t="n">
-        <v>6.5</v>
+        <v>23.8</v>
       </c>
       <c r="V66" t="n">
-        <v>17.6</v>
+        <v>0.32</v>
       </c>
       <c r="W66" t="n">
-        <v>2</v>
+        <v>23.8731856378915</v>
       </c>
       <c r="X66" t="n">
-        <v>21.15</v>
+        <v>23.0715863589186</v>
       </c>
       <c r="Y66" t="n">
-        <v>0.328063241106719</v>
+        <v>0</v>
       </c>
       <c r="Z66" t="n">
-        <v>21.2312197606315</v>
+        <v>1</v>
       </c>
       <c r="AA66" t="n">
-        <v>20.4044886078792</v>
+        <v>0</v>
       </c>
       <c r="AB66" t="n">
         <v>0</v>
@@ -8573,32 +8030,21 @@
         <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI66" t="n">
         <v>0</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>142</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="AK66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8613,85 +8059,85 @@
         <v>82.4293631328111</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>25.1428571428571</v>
       </c>
       <c r="E67" t="n">
-        <v>25.1428571428571</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>50</v>
+        <v>633</v>
       </c>
       <c r="I67" t="n">
-        <v>4120</v>
+        <v>324</v>
       </c>
       <c r="J67" t="n">
-        <v>0</v>
+        <v>393</v>
       </c>
       <c r="K67" t="n">
-        <v>633</v>
+        <v>1350</v>
       </c>
       <c r="L67" t="n">
-        <v>324</v>
+        <v>81</v>
       </c>
       <c r="M67" t="n">
-        <v>393</v>
+        <v>28</v>
       </c>
       <c r="N67" t="n">
-        <v>1350</v>
+        <v>12</v>
       </c>
       <c r="O67" t="n">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="P67" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>22.3</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W67" t="n">
-        <v>1</v>
+        <v>23.554876496053</v>
       </c>
       <c r="X67" t="n">
-        <v>22.3</v>
+        <v>22.8163986665956</v>
       </c>
       <c r="Y67" t="n">
-        <v>0.297709923664122</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>23.554876496053</v>
+        <v>1</v>
       </c>
       <c r="AA67" t="n">
-        <v>22.8163986665956</v>
+        <v>0</v>
       </c>
       <c r="AB67" t="n">
         <v>0</v>
       </c>
       <c r="AC67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -8700,27 +8146,18 @@
         <v>0</v>
       </c>
       <c r="AG67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI67" t="n">
         <v>0</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="AK67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL67" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM67" t="n">
-        <v>94</v>
-      </c>
-      <c r="AN67" t="n">
         <v>210</v>
       </c>
     </row>
